--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$73</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2672" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -610,6 +613,217 @@
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN].reasonCOde</t>
   </si>
   <si>
+    <t>MedicationStatement.statusReason.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>MedicationStatement.statusReason.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>MedicationStatement.category</t>
   </si>
   <si>
@@ -629,6 +843,39 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationStatement.category.text</t>
   </si>
   <si>
     <t>MedicationStatement.medication[x]</t>
@@ -688,6 +935,72 @@
     <t>http://doh.gov.ph/fhir/ph-core/ValueSet/drugs-vs</t>
   </si>
   <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.system</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.version</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.code</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.display</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x]:medicationCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>MedicationStatement.medication[x].text</t>
+  </si>
+  <si>
     <t>MedicationStatement.subject</t>
   </si>
   <si>
@@ -839,6 +1152,39 @@
   </si>
   <si>
     <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationStatement.reasonCode.text</t>
   </si>
   <si>
     <t>MedicationStatement.reasonReference</t>
@@ -1027,6 +1373,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1202,11 +1563,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.37890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="68.87109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1233,7 +1594,7 @@
     <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1243,7 +1604,7 @@
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="120.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1368,7 +1729,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1482,7 +1843,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -1596,7 +1957,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -1708,7 +2069,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>102</v>
       </c>
@@ -1822,7 +2183,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>108</v>
       </c>
@@ -1936,7 +2297,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2050,7 +2411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
@@ -2164,7 +2525,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -2278,7 +2639,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -2394,7 +2755,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -2508,7 +2869,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2622,7 +2983,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -2736,7 +3097,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -2869,7 +3230,7 @@
         <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>78</v>
@@ -2964,7 +3325,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>188</v>
       </c>
@@ -2989,16 +3350,16 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3025,32 +3386,32 @@
         <v>78</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="Z16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3061,7 +3422,7 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3070,29 +3431,29 @@
         <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3101,19 +3462,19 @@
         <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3139,50 +3500,52 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3190,14 +3553,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3206,10 +3567,10 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>78</v>
@@ -3218,18 +3579,20 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3277,13 +3640,13 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>78</v>
@@ -3292,28 +3655,26 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3331,20 +3692,18 @@
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3369,11 +3728,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3391,10 +3752,10 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3403,38 +3764,38 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
@@ -3443,18 +3804,20 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3491,51 +3854,51 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3558,16 +3921,20 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3615,7 +3982,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3630,24 +3997,24 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3670,16 +4037,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3729,7 +4096,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3744,24 +4111,24 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3775,7 +4142,7 @@
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -3784,16 +4151,18 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -3841,7 +4210,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3859,21 +4228,21 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3893,19 +4262,21 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -3953,7 +4324,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3971,21 +4342,21 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3996,7 +4367,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4005,21 +4376,23 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4067,13 +4440,13 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
@@ -4085,21 +4458,21 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4110,7 +4483,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4119,21 +4492,23 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4157,13 +4532,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4181,13 +4556,13 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
@@ -4196,24 +4571,24 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4224,29 +4599,27 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4271,13 +4644,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4295,13 +4668,13 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
@@ -4310,24 +4683,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4338,7 +4711,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4350,13 +4723,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>270</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>271</v>
+        <v>190</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4407,25 +4780,25 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -4434,16 +4807,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4462,16 +4835,16 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>276</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4509,19 +4882,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4533,22 +4906,5060 @@
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+      <c r="Z39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AC39" s="2"/>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y41" s="2"/>
+      <c r="Z41" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN73">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI72">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$45</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2672" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="326">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -679,127 +679,6 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>MedicationStatement.statusReason.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationStatement.statusReason.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationStatement.statusReason.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>MedicationStatement.statusReason.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>MedicationStatement.statusReason.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>MedicationStatement.statusReason.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>MedicationStatement.statusReason.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>MedicationStatement.statusReason.text</t>
   </si>
   <si>
@@ -852,27 +731,6 @@
   </si>
   <si>
     <t>MedicationStatement.category.coding</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationStatement.category.coding.userSelected</t>
   </si>
   <si>
     <t>MedicationStatement.category.text</t>
@@ -953,48 +811,6 @@
     <t>MedicationStatement.medication[x].coding</t>
   </si>
   <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.id</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.system</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.version</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.code</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.display</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x]:medicationCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>MedicationStatement.medication[x].coding.userSelected</t>
-  </si>
-  <si>
     <t>MedicationStatement.medication[x]:medicationCodeableConcept.text</t>
   </si>
   <si>
@@ -1161,27 +977,6 @@
   </si>
   <si>
     <t>MedicationStatement.reasonCode.coding</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationStatement.reasonCode.coding.userSelected</t>
   </si>
   <si>
     <t>MedicationStatement.reasonCode.text</t>
@@ -1563,11 +1358,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN73"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.87109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.68359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="60.56640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.37890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3667,7 +3462,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>209</v>
       </c>
@@ -3686,25 +3481,29 @@
         <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3752,7 +3551,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3764,60 +3563,58 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3842,52 +3639,52 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -3895,10 +3692,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3918,23 +3715,19 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3982,7 +3775,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3994,38 +3787,38 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
@@ -4034,19 +3827,19 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4084,43 +3877,43 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
@@ -4139,7 +3932,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>90</v>
@@ -4151,17 +3944,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4210,13 +4005,13 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
@@ -4228,21 +4023,21 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4256,7 +4051,7 @@
         <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>78</v>
@@ -4268,14 +4063,16 @@
         <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4324,7 +4121,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4342,21 +4139,21 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>239</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4364,7 +4161,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
@@ -4379,20 +4176,18 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4416,34 +4211,32 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>89</v>
@@ -4455,26 +4248,28 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4495,20 +4290,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4556,10 +4349,10 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>89</v>
@@ -4571,26 +4364,28 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4614,12 +4409,14 @@
         <v>179</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4646,11 +4443,9 @@
       <c r="X27" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y27" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4668,10 +4463,10 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4683,13 +4478,13 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4697,10 +4492,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4809,10 +4604,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4923,10 +4718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5037,12 +4832,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5056,25 +4851,29 @@
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5122,7 +4921,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5134,38 +4933,38 @@
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
@@ -5174,20 +4973,18 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>136</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5224,51 +5021,51 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>199</v>
+        <v>254</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5291,20 +5088,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>263</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
@@ -5352,7 +5145,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5367,24 +5160,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5407,16 +5200,16 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5466,7 +5259,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5481,24 +5274,24 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5512,7 +5305,7 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -5521,18 +5314,16 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>228</v>
+        <v>279</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5580,7 +5371,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5598,21 +5389,21 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5632,21 +5423,19 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>283</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>236</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5694,7 +5483,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5712,21 +5501,21 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5737,7 +5526,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -5746,23 +5535,21 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5810,13 +5597,13 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
@@ -5828,21 +5615,21 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5853,32 +5640,30 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5902,13 +5687,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>298</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -5926,13 +5711,13 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
@@ -5941,24 +5726,24 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5966,7 +5751,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -5978,20 +5763,18 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6016,32 +5799,34 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -6050,16 +5835,16 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6067,23 +5852,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6092,19 +5875,19 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>289</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6142,40 +5925,40 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6183,14 +5966,12 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6199,7 +5980,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>90</v>
@@ -6211,18 +5992,20 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>278</v>
+        <v>203</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6246,11 +6029,13 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6268,13 +6053,13 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
@@ -6283,24 +6068,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>285</v>
+        <v>207</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6314,25 +6099,29 @@
         <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6380,7 +6169,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6392,31 +6181,31 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6435,16 +6224,16 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>138</v>
+        <v>311</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6482,19 +6271,19 @@
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>199</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6506,27 +6295,27 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6540,29 +6329,25 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>201</v>
+        <v>315</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>316</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6610,7 +6395,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>314</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6625,24 +6410,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>207</v>
+        <v>319</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6653,7 +6438,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -6665,15 +6450,17 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>189</v>
+        <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>190</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6722,3227 +6509,35 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN73" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN73">
+  <autoFilter ref="A1:AN45">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9952,7 +6547,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI44">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-medicationstatement.xlsx
+++ b/dev/StructureDefinition-ph-core-medicationstatement.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
